--- a/EIANN/data/supplementary_tables/Table_S6_mnist_hyperparams_part2.xlsx
+++ b/EIANN/data/supplementary_tables/Table_S6_mnist_hyperparams_part2.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F43"/>
+  <dimension ref="A1:G43"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -436,31 +436,35 @@
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>Fixed DendI 
-(random)</t>
+          <t>Dend. Target Prop.
+(Fixed DendI)</t>
         </is>
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>Learned DendI 
-(local backprop)</t>
+          <t>Dend. Target Prop.
+(Learned DendI, BP)</t>
         </is>
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>Dendritic 
-Target Propagation</t>
+          <t>Dend. Target Prop
+(Learned DendI, Hebb)</t>
         </is>
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>Temp. Contrastive 
-Hebb</t>
+          <t>Sup. TCH</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>BCM</t>
+          <t>Sup. BCM</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>Unsup. BCM</t>
         </is>
       </c>
     </row>
@@ -485,6 +489,9 @@
       <c r="F2" t="n">
         <v>1.577752606628473</v>
       </c>
+      <c r="G2" t="n">
+        <v>1.052683452178838</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -507,6 +514,9 @@
       <c r="F3" t="n">
         <v>0.005276417437133462</v>
       </c>
+      <c r="G3" t="n">
+        <v>0.005125496762844439</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -529,6 +539,9 @@
       <c r="F4" t="n">
         <v>0.7547901746981226</v>
       </c>
+      <c r="G4" t="n">
+        <v>1.268014634921803</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -551,6 +564,11 @@
       <c r="F5" t="n">
         <v>0.1169093463605384</v>
       </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -573,6 +591,11 @@
       <c r="F6" t="n">
         <v>0.04845476706284365</v>
       </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -595,6 +618,11 @@
       <c r="F7" t="n">
         <v>0.4654326399357083</v>
       </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -617,6 +645,9 @@
       <c r="F8" t="n">
         <v>1.54370592606602</v>
       </c>
+      <c r="G8" t="n">
+        <v>0.9876413009339409</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -639,6 +670,9 @@
       <c r="F9" t="n">
         <v>0.9798467535193344</v>
       </c>
+      <c r="G9" t="n">
+        <v>1.641720136020369</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -661,6 +695,9 @@
       <c r="F10" t="n">
         <v>0.5321690501979497</v>
       </c>
+      <c r="G10" t="n">
+        <v>1.10450719910091</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -689,6 +726,11 @@
           <t>-</t>
         </is>
       </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -717,6 +759,11 @@
           <t>-</t>
         </is>
       </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -739,6 +786,9 @@
       <c r="F13" t="n">
         <v>0.04060862080020256</v>
       </c>
+      <c r="G13" t="n">
+        <v>1.347805722791249</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -761,6 +811,9 @@
       <c r="F14" t="n">
         <v>0.005276417437133462</v>
       </c>
+      <c r="G14" t="n">
+        <v>0.005125496762844439</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -783,6 +836,9 @@
       <c r="F15" t="n">
         <v>0.1938236003570908</v>
       </c>
+      <c r="G15" t="n">
+        <v>0.5813913217961937</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -805,6 +861,11 @@
       <c r="F16" t="n">
         <v>0.840872013463585</v>
       </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -827,6 +888,11 @@
       <c r="F17" t="n">
         <v>0.04845476706284365</v>
       </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -849,6 +915,11 @@
       <c r="F18" t="n">
         <v>1.342176931062382</v>
       </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -871,6 +942,9 @@
       <c r="F19" t="n">
         <v>0.2265322545186243</v>
       </c>
+      <c r="G19" t="n">
+        <v>1.624800703347681</v>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -893,6 +967,9 @@
       <c r="F20" t="n">
         <v>0.5136096108519347</v>
       </c>
+      <c r="G20" t="n">
+        <v>0.301471500541645</v>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -915,6 +992,9 @@
       <c r="F21" t="n">
         <v>0.8106845893034254</v>
       </c>
+      <c r="G21" t="n">
+        <v>1.07845820629407</v>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -943,6 +1023,11 @@
           <t>-</t>
         </is>
       </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -971,6 +1056,11 @@
           <t>-</t>
         </is>
       </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -993,6 +1083,9 @@
       <c r="F24" t="n">
         <v>1.704895812714677</v>
       </c>
+      <c r="G24" t="n">
+        <v>0.6520065253237064</v>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -1015,6 +1108,9 @@
       <c r="F25" t="n">
         <v>0.002069970626003369</v>
       </c>
+      <c r="G25" t="n">
+        <v>0.01190343395460727</v>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -1037,6 +1133,9 @@
       <c r="F26" t="n">
         <v>0.03236590828898294</v>
       </c>
+      <c r="G26" t="n">
+        <v>0.7004104131893767</v>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -1059,6 +1158,9 @@
       <c r="F27" t="n">
         <v>0.5258723114460294</v>
       </c>
+      <c r="G27" t="n">
+        <v>0.9274644582522223</v>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
@@ -1081,6 +1183,9 @@
       <c r="F28" t="n">
         <v>5.965952820948539</v>
       </c>
+      <c r="G28" t="n">
+        <v>1.428565955626174</v>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -1103,6 +1208,9 @@
       <c r="F29" t="n">
         <v>1.131346606025058</v>
       </c>
+      <c r="G29" t="n">
+        <v>1.180799672135971</v>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
@@ -1127,6 +1235,11 @@
       <c r="F30" t="n">
         <v>0.01182836312981857</v>
       </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
@@ -1151,6 +1264,11 @@
       <c r="F31" t="n">
         <v>0.02337923963359796</v>
       </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
@@ -1175,6 +1293,11 @@
       <c r="F32" t="n">
         <v>0.01182836312981857</v>
       </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
@@ -1199,6 +1322,11 @@
       <c r="F33" t="n">
         <v>0.02337923963359796</v>
       </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
@@ -1225,6 +1353,11 @@
       <c r="F34" t="n">
         <v>4.006479344944808</v>
       </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
@@ -1251,6 +1384,11 @@
       <c r="F35" t="n">
         <v>2.247922610423426</v>
       </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
@@ -1277,6 +1415,11 @@
       <c r="F36" t="n">
         <v>3.077817655049544</v>
       </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
@@ -1303,6 +1446,11 @@
       <c r="F37" t="n">
         <v>2.250194789554047</v>
       </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
@@ -1333,6 +1481,9 @@
       <c r="F38" t="n">
         <v>14.47002100871862</v>
       </c>
+      <c r="G38" t="n">
+        <v>27.80474881390654</v>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
@@ -1363,6 +1514,9 @@
       <c r="F39" t="n">
         <v>0.02150183978334577</v>
       </c>
+      <c r="G39" t="n">
+        <v>0.02033990374023492</v>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
@@ -1393,6 +1547,9 @@
       <c r="F40" t="n">
         <v>14.47002100871862</v>
       </c>
+      <c r="G40" t="n">
+        <v>27.80474881390654</v>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
@@ -1423,6 +1580,9 @@
       <c r="F41" t="n">
         <v>0.02150183978334577</v>
       </c>
+      <c r="G41" t="n">
+        <v>0.02033990374023492</v>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
@@ -1453,6 +1613,11 @@
       <c r="F42" t="n">
         <v>21.6775826883819</v>
       </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
@@ -1482,6 +1647,11 @@
       </c>
       <c r="F43" t="n">
         <v>0.1593672622296362</v>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
   </sheetData>

--- a/EIANN/data/supplementary_tables/Table_S6_mnist_hyperparams_part2.xlsx
+++ b/EIANN/data/supplementary_tables/Table_S6_mnist_hyperparams_part2.xlsx
@@ -471,7 +471,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Winit (H1)</t>
+          <t>W_init (H1)</t>
         </is>
       </c>
       <c r="B2" t="n">
@@ -521,7 +521,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Yinit (SomaI, H1)</t>
+          <t>Y_init (SomaI, H1)</t>
         </is>
       </c>
       <c r="B4" t="n">
@@ -546,7 +546,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Yinit (DendI, H1)</t>
+          <t>Y_init (DendI, H1)</t>
         </is>
       </c>
       <c r="B5" t="n">
@@ -600,7 +600,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Bscale (H1)</t>
+          <t>B_scale (H1)</t>
         </is>
       </c>
       <c r="B7" t="n">
@@ -627,7 +627,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Winit (SomaI, H1)</t>
+          <t>W_init (SomaI, H1)</t>
         </is>
       </c>
       <c r="B8" t="n">
@@ -652,7 +652,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Qinit (SomaI, H1)</t>
+          <t>Q_init (SomaI, H1)</t>
         </is>
       </c>
       <c r="B9" t="n">
@@ -677,7 +677,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Rinit (SomaI, H1)</t>
+          <t>R_init (SomaI, H1)</t>
         </is>
       </c>
       <c r="B10" t="n">
@@ -702,7 +702,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Qinit (DendI, H1)</t>
+          <t>Q_init (DendI, H1)</t>
         </is>
       </c>
       <c r="B11" t="n">
@@ -735,7 +735,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Rinit (DendI, H1)</t>
+          <t>R_init (DendI, H1)</t>
         </is>
       </c>
       <c r="B12" t="n">
@@ -768,7 +768,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Winit (H2)</t>
+          <t>W_init (H2)</t>
         </is>
       </c>
       <c r="B13" t="n">
@@ -818,7 +818,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Yinit (SomaI, H2)</t>
+          <t>Y_init (SomaI, H2)</t>
         </is>
       </c>
       <c r="B15" t="n">
@@ -843,7 +843,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Yinit (DendI, H2)</t>
+          <t>Y_init (DendI, H2)</t>
         </is>
       </c>
       <c r="B16" t="n">
@@ -897,7 +897,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Bscale (H2)</t>
+          <t>B_scale (H2)</t>
         </is>
       </c>
       <c r="B18" t="n">
@@ -924,7 +924,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Winit (SomaI, H2)</t>
+          <t>W_init (SomaI, H2)</t>
         </is>
       </c>
       <c r="B19" t="n">
@@ -949,7 +949,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Qinit (SomaI, H2)</t>
+          <t>Q_init (SomaI, H2)</t>
         </is>
       </c>
       <c r="B20" t="n">
@@ -974,7 +974,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Rinit (SomaI, H2)</t>
+          <t>R_init (SomaI, H2)</t>
         </is>
       </c>
       <c r="B21" t="n">
@@ -999,7 +999,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Qinit (DendI, H2)</t>
+          <t>Q_init (DendI, H2)</t>
         </is>
       </c>
       <c r="B22" t="n">
@@ -1032,7 +1032,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Rinit (DendI, H2)</t>
+          <t>R_init (DendI, H2)</t>
         </is>
       </c>
       <c r="B23" t="n">
@@ -1065,7 +1065,7 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Winit (Output)</t>
+          <t>W_init (Output)</t>
         </is>
       </c>
       <c r="B24" t="n">
@@ -1115,7 +1115,7 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Yinit (SomaI, Output)</t>
+          <t>Y_init (SomaI, Output)</t>
         </is>
       </c>
       <c r="B26" t="n">
@@ -1140,7 +1140,7 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Winit (SomaI, Output)</t>
+          <t>W_init (SomaI, Output)</t>
         </is>
       </c>
       <c r="B27" t="n">
@@ -1165,7 +1165,7 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Qinit (SomaI, Output)</t>
+          <t>Q_init (SomaI, Output)</t>
         </is>
       </c>
       <c r="B28" t="n">
@@ -1190,7 +1190,7 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Rinit (SomaI, Output)</t>
+          <t>R_init (SomaI, Output)</t>
         </is>
       </c>
       <c r="B29" t="n">
@@ -1331,7 +1331,7 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Qsum (DendI, H1)</t>
+          <t>Q_sum (DendI, H1)</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -1362,7 +1362,7 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Rsum (DendI, H1)</t>
+          <t>R_sum (DendI, H1)</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -1393,7 +1393,7 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Qsum (DendI, H2)</t>
+          <t>Q_sum (DendI, H2)</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -1424,7 +1424,7 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Rsum (DendI, H2)</t>
+          <t>R_sum (DendI, H2)</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -1455,7 +1455,7 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>τθ, (H1)</t>
+          <t>τ_θ, (H1)</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -1521,7 +1521,7 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>τθ, (H2)</t>
+          <t>τ_θ, (H2)</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -1587,7 +1587,7 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>τθ, (Output)</t>
+          <t>τ_θ, (Output)</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
